--- a/attendance/python-script/all_users_main_branch.xlsx
+++ b/attendance/python-script/all_users_main_branch.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1373"/>
+  <dimension ref="A1:E1380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37487,6 +37487,195 @@
         </is>
       </c>
     </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Emanfatima</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Muhammadali</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>Furqan</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>Harryson</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>Jhonson</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>Tehmina</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendance/python-script/all_users_main_branch.xlsx
+++ b/attendance/python-script/all_users_main_branch.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1380"/>
+  <dimension ref="A1:E1384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37676,6 +37676,114 @@
         </is>
       </c>
     </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>Mudassir</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Qasim</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>1382</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Irfan</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>1383</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Ishaq</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendance/python-script/all_users_main_branch.xlsx
+++ b/attendance/python-script/all_users_main_branch.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1384"/>
+  <dimension ref="A1:E1416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37784,6 +37784,870 @@
         </is>
       </c>
     </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>Rahimakhan</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Hussainalikhan</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Sherazali</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Muneeb</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Tariqjamil</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Farrukhmir</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Khateja</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>1391</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Sufiyanahmed</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Mwaize</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>1393</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Huzaifa</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>1394</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>Abdullah</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Murtaza</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>Hassam</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>Liaqatullah</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>Umerzahid</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>Umerali</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>Ahmad</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Mohsin</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Mantasha</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>Muneeb</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Hamzatariq</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>Abdulmuneam</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>Sahil</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>1407</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>Ahtisham</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>Bilal</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>1409</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>Waleed</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>Saqibali</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>1411</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>Mhammad</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>hassan</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>Wajahat</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>Shahmeer</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Arooj</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendance/python-script/all_users_main_branch.xlsx
+++ b/attendance/python-script/all_users_main_branch.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1416"/>
+  <dimension ref="A1:E1441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38648,6 +38648,681 @@
         </is>
       </c>
     </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>Rafay</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>1417</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Ahsan</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>Mohibatif</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>1419</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>Meesum</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>Moiz</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>Fahad</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>1422</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>Adil</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>1423</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>Abdulraheem</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Masadullah</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>Abdulwahab</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>Alishah</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>1427</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Mohidhadi</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Zeeshan</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>Mubashir</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Uqba</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>1431</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>Abdulhadi</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Shalook</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>1433</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>Bakhtawar</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>Noor</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>Farhad</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>Ahmad</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>1437</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>Zia</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>Huzaifa</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>Abdulahad</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>Muhammadanas</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendance/python-script/all_users_main_branch.xlsx
+++ b/attendance/python-script/all_users_main_branch.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1441"/>
+  <dimension ref="A1:E1447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39323,6 +39323,168 @@
         </is>
       </c>
     </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>1441</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>Mujtaba</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>Rahman</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>Zaeem</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>Hashirabbsi</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>Shahzaib</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>1446</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>Awaisabbasi</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendance/python-script/all_users_main_branch.xlsx
+++ b/attendance/python-script/all_users_main_branch.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1447"/>
+  <dimension ref="A1:E1477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39485,6 +39485,816 @@
         </is>
       </c>
     </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>Muhammadfahad</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>Rayna</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>Fallahmubarak</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>Abdullah</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>1451</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>Ahmedsuleman</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>Iqrachaudhary</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>Zulqarnainhaider</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>1454</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>Affanbinnaveed</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>1455</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>Hamidiqbal</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>Alihaider</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>1457</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>Anasmishwani</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>1458</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>Aqsaiftikhar</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>1459</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>Zohairali</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>Huzaifa</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>Ayubbasharat</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>Muhammadfahad</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>Ansnouman</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>1465</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>Rabbia</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>Irfan</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>Mali</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>Usman</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>1469</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>Sairarashid</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>1470</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>Umairshahid</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>Sajid</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>Zainulabadin</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>1473</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>Daniyalqureshi</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>1474</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>Eman</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>Zohaib</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>Main Branch</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>203.215.161.244</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
